--- a/强基查证清单.xlsx
+++ b/强基查证清单.xlsx
@@ -3011,11 +3011,7 @@
           <t>文史哲综合</t>
         </is>
       </c>
-      <c r="L9" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L9" s="15" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -3066,11 +3062,7 @@
           <t>文史哲综合</t>
         </is>
       </c>
-      <c r="L10" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L10" s="15" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -3121,11 +3113,7 @@
           <t>数学+物理</t>
         </is>
       </c>
-      <c r="L11" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L11" s="15" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -3176,11 +3164,7 @@
           <t>数学+物理</t>
         </is>
       </c>
-      <c r="L12" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L12" s="15" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -3231,11 +3215,7 @@
           <t>数学+物理</t>
         </is>
       </c>
-      <c r="L13" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L13" s="15" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -3286,11 +3266,7 @@
           <t>数学+物理</t>
         </is>
       </c>
-      <c r="L14" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L14" s="15" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -3341,11 +3317,7 @@
           <t>数学+物理</t>
         </is>
       </c>
-      <c r="L15" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L15" s="15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -3396,11 +3368,7 @@
           <t>数学+物理</t>
         </is>
       </c>
-      <c r="L16" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L16" s="15" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -3451,11 +3419,7 @@
           <t>数学+化学</t>
         </is>
       </c>
-      <c r="L17" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L17" s="15" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -3506,11 +3470,7 @@
           <t>数学+化学</t>
         </is>
       </c>
-      <c r="L18" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L18" s="15" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -3561,11 +3521,7 @@
           <t>数学+化学</t>
         </is>
       </c>
-      <c r="L19" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L19" s="15" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -3616,11 +3572,7 @@
           <t>数理探究</t>
         </is>
       </c>
-      <c r="L20" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L20" s="15" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -3671,11 +3623,7 @@
           <t>数理探究</t>
         </is>
       </c>
-      <c r="L21" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L21" s="15" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -3726,11 +3674,7 @@
           <t>数理探究</t>
         </is>
       </c>
-      <c r="L22" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L22" s="15" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -3781,11 +3725,7 @@
           <t>数理探究</t>
         </is>
       </c>
-      <c r="L23" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L23" s="15" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -3836,11 +3776,7 @@
           <t>数理探究</t>
         </is>
       </c>
-      <c r="L24" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L24" s="15" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -3918,11 +3854,7 @@
           <t>阅读表达</t>
         </is>
       </c>
-      <c r="L26" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L26" s="15" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -3959,11 +3891,7 @@
           <t>阅读表达</t>
         </is>
       </c>
-      <c r="L27" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L27" s="15" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -4009,16 +3937,8 @@
           <t>试验班</t>
         </is>
       </c>
-      <c r="K28" s="15" t="inlineStr">
-        <is>
-          <t>阅读表达</t>
-        </is>
-      </c>
-      <c r="L28" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="K28" s="15" t="inlineStr"/>
+      <c r="L28" s="15" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -4064,16 +3984,8 @@
           <t>试验班</t>
         </is>
       </c>
-      <c r="K29" s="15" t="inlineStr">
-        <is>
-          <t>阅读表达</t>
-        </is>
-      </c>
-      <c r="L29" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="K29" s="15" t="inlineStr"/>
+      <c r="L29" s="15" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -4239,16 +4151,8 @@
           <t>试验班</t>
         </is>
       </c>
-      <c r="K33" s="15" t="inlineStr">
-        <is>
-          <t>阅读表达</t>
-        </is>
-      </c>
-      <c r="L33" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="K33" s="15" t="inlineStr"/>
+      <c r="L33" s="15" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
@@ -4334,16 +4238,8 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="K35" s="15" t="inlineStr">
-        <is>
-          <t>阅读表达</t>
-        </is>
-      </c>
-      <c r="L35" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="K35" s="15" t="inlineStr"/>
+      <c r="L35" s="15" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -4394,11 +4290,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L36" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L36" s="15" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -4489,11 +4381,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L38" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L38" s="15" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -4584,11 +4472,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L40" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L40" s="15" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
@@ -4639,11 +4523,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L41" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L41" s="15" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -4734,11 +4614,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L43" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L43" s="15" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -4789,11 +4665,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L44" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L44" s="15" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -4882,11 +4754,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L46" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L46" s="15" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -4937,11 +4805,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L47" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L47" s="15" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -4992,11 +4856,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L48" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L48" s="15" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -5047,11 +4907,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L49" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L49" s="15" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -5102,11 +4958,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L50" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L50" s="15" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -5157,11 +5009,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L51" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L51" s="15" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -5212,11 +5060,7 @@
           <t>数学、化学</t>
         </is>
       </c>
-      <c r="L52" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L52" s="15" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -5267,11 +5111,7 @@
           <t>数学、化学</t>
         </is>
       </c>
-      <c r="L53" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L53" s="15" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -5322,11 +5162,7 @@
           <t>数学、化学</t>
         </is>
       </c>
-      <c r="L54" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L54" s="15" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -5377,11 +5213,7 @@
           <t>数学、化学</t>
         </is>
       </c>
-      <c r="L55" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L55" s="15" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -5418,11 +5250,7 @@
           <t>数学、化学</t>
         </is>
       </c>
-      <c r="L56" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L56" s="15" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -5473,11 +5301,7 @@
           <t>数学、化学</t>
         </is>
       </c>
-      <c r="L57" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L57" s="15" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -5583,11 +5407,7 @@
           <t>语文、历史</t>
         </is>
       </c>
-      <c r="L59" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L59" s="15" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -5638,11 +5458,7 @@
           <t>语文、历史</t>
         </is>
       </c>
-      <c r="L60" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L60" s="15" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -5693,11 +5509,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L61" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L61" s="15" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
@@ -5788,11 +5600,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L63" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L63" s="15" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
@@ -5843,11 +5651,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L64" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L64" s="15" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -5898,11 +5702,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L65" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L65" s="15" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
@@ -5953,11 +5753,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L66" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L66" s="15" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
     </row>
     <row r="67">
@@ -6008,11 +5804,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L67" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L67" s="15" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
     </row>
     <row r="68">
@@ -6063,11 +5855,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L68" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L68" s="15" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
     </row>
     <row r="69">
@@ -6118,11 +5906,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L69" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L69" s="15" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
     </row>
     <row r="70">
@@ -6173,11 +5957,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L70" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L70" s="15" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
@@ -6228,11 +6008,7 @@
           <t>语文、历史</t>
         </is>
       </c>
-      <c r="L71" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L71" s="15" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
@@ -6283,11 +6059,7 @@
           <t>数理综合</t>
         </is>
       </c>
-      <c r="L72" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L72" s="15" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
     </row>
     <row r="73">
@@ -6338,11 +6110,7 @@
           <t>数理综合</t>
         </is>
       </c>
-      <c r="L73" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L73" s="15" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
@@ -6393,11 +6161,7 @@
           <t>数理综合</t>
         </is>
       </c>
-      <c r="L74" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L74" s="15" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
@@ -6446,11 +6210,7 @@
           <t>数理综合</t>
         </is>
       </c>
-      <c r="L75" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L75" s="15" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
     </row>
     <row r="76">
@@ -6501,11 +6261,7 @@
           <t>化学</t>
         </is>
       </c>
-      <c r="L76" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L76" s="15" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
@@ -6556,11 +6312,7 @@
           <t>化学</t>
         </is>
       </c>
-      <c r="L77" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L77" s="15" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
     </row>
     <row r="78">
@@ -6611,11 +6363,7 @@
           <t>数理综合</t>
         </is>
       </c>
-      <c r="L78" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L78" s="15" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
     </row>
     <row r="79">
@@ -6706,11 +6454,7 @@
           <t>数理综合</t>
         </is>
       </c>
-      <c r="L80" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L80" s="15" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
     </row>
     <row r="81">
@@ -6761,11 +6505,7 @@
           <t>数理化综合</t>
         </is>
       </c>
-      <c r="L81" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L81" s="15" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
     </row>
     <row r="82">
@@ -6936,11 +6676,7 @@
           <t>数理化综合</t>
         </is>
       </c>
-      <c r="L85" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L85" s="15" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
     </row>
     <row r="86">
@@ -7071,11 +6807,7 @@
           <t>数理化综合</t>
         </is>
       </c>
-      <c r="L88" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L88" s="15" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
     </row>
     <row r="89">
@@ -7126,11 +6858,7 @@
           <t>数理化综合</t>
         </is>
       </c>
-      <c r="L89" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L89" s="15" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
@@ -7181,11 +6909,7 @@
           <t>文史哲综合</t>
         </is>
       </c>
-      <c r="L90" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L90" s="15" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
     </row>
     <row r="91">
@@ -7236,11 +6960,7 @@
           <t>文史哲综合</t>
         </is>
       </c>
-      <c r="L91" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L91" s="15" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
     </row>
     <row r="92">
@@ -7291,11 +7011,7 @@
           <t>数学及航空航天知识基础、数学拔高</t>
         </is>
       </c>
-      <c r="L92" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L92" s="15" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
     </row>
     <row r="93">
@@ -7346,11 +7062,7 @@
           <t>数学及航空航天知识基础、化学拔高</t>
         </is>
       </c>
-      <c r="L93" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L93" s="15" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
     </row>
     <row r="94">
@@ -7401,11 +7113,7 @@
           <t>数学及航空航天知识基础、物理拔高</t>
         </is>
       </c>
-      <c r="L94" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L94" s="15" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
     </row>
     <row r="95">
@@ -7456,11 +7164,7 @@
           <t>数学及航空航天知识基础、物理拔高</t>
         </is>
       </c>
-      <c r="L95" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L95" s="15" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
     </row>
     <row r="96">
@@ -7511,11 +7215,7 @@
           <t>数学及航空航天知识基础、物理拔高</t>
         </is>
       </c>
-      <c r="L96" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L96" s="15" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
     </row>
     <row r="97">
@@ -7621,11 +7321,7 @@
           <t>数学及航空航天知识基础、物理拔高</t>
         </is>
       </c>
-      <c r="L98" s="15" t="inlineStr">
-        <is>
-          <t>量子信息</t>
-        </is>
-      </c>
+      <c r="L98" s="15" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
     </row>
     <row r="99">
@@ -7676,11 +7372,7 @@
           <t>数学及航空航天知识基础、物理拔高</t>
         </is>
       </c>
-      <c r="L99" s="15" t="inlineStr">
-        <is>
-          <t>量子信息</t>
-        </is>
-      </c>
+      <c r="L99" s="15" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
@@ -7811,11 +7503,7 @@
           <t>数理科技相关</t>
         </is>
       </c>
-      <c r="L102" s="15" t="inlineStr">
-        <is>
-          <t>量子信息</t>
-        </is>
-      </c>
+      <c r="L102" s="15" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
     </row>
     <row r="103">
@@ -7921,11 +7609,7 @@
           <t>文史哲相关</t>
         </is>
       </c>
-      <c r="L104" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L104" s="15" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
     </row>
     <row r="105">
@@ -8016,11 +7700,7 @@
           <t>文史哲相关</t>
         </is>
       </c>
-      <c r="L106" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L106" s="15" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
     </row>
     <row r="107">
@@ -8071,11 +7751,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L107" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L107" s="15" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
     </row>
     <row r="108">
@@ -8126,11 +7802,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L108" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L108" s="15" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
     </row>
     <row r="109">
@@ -8181,11 +7853,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L109" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L109" s="15" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
     </row>
     <row r="110">
@@ -8236,11 +7904,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L110" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L110" s="15" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
     </row>
     <row r="111">
@@ -8291,11 +7955,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L111" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L111" s="15" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
     </row>
     <row r="112">
@@ -8346,11 +8006,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L112" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L112" s="15" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
     </row>
     <row r="113">
@@ -8839,11 +8495,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L124" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L124" s="15" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
     </row>
     <row r="125">
@@ -8894,11 +8546,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L125" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L125" s="15" t="inlineStr"/>
       <c r="M125" t="inlineStr"/>
     </row>
     <row r="126">
@@ -9044,11 +8692,7 @@
           <t>数学、语文、历史</t>
         </is>
       </c>
-      <c r="L128" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L128" s="15" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
     </row>
     <row r="129">
@@ -9099,11 +8743,7 @@
           <t>数学、语文、历史</t>
         </is>
       </c>
-      <c r="L129" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L129" s="15" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
     </row>
     <row r="130">
@@ -9154,11 +8794,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L130" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L130" s="15" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
     </row>
     <row r="131">
@@ -9369,11 +9005,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L135" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L135" s="15" t="inlineStr"/>
       <c r="M135" t="inlineStr"/>
     </row>
     <row r="136">
@@ -9544,11 +9176,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L139" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L139" s="15" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
     </row>
     <row r="140">
@@ -9879,11 +9507,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L147" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L147" s="15" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
     </row>
     <row r="148">
@@ -9934,11 +9558,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L148" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L148" s="15" t="inlineStr"/>
       <c r="M148" t="inlineStr"/>
     </row>
     <row r="149">
@@ -10164,11 +9784,7 @@
           <t>语文、英语、历史</t>
         </is>
       </c>
-      <c r="L153" s="15" t="inlineStr">
-        <is>
-          <t>八年制</t>
-        </is>
-      </c>
+      <c r="L153" s="15" t="inlineStr"/>
       <c r="M153" t="inlineStr"/>
     </row>
     <row r="154">
@@ -10219,11 +9835,7 @@
           <t>语文、英语、历史</t>
         </is>
       </c>
-      <c r="L154" s="15" t="inlineStr">
-        <is>
-          <t>八年制</t>
-        </is>
-      </c>
+      <c r="L154" s="15" t="inlineStr"/>
       <c r="M154" t="inlineStr"/>
     </row>
     <row r="155">
@@ -10274,11 +9886,7 @@
           <t>语文、英语、历史</t>
         </is>
       </c>
-      <c r="L155" s="15" t="inlineStr">
-        <is>
-          <t>八年制</t>
-        </is>
-      </c>
+      <c r="L155" s="15" t="inlineStr"/>
       <c r="M155" t="inlineStr"/>
     </row>
     <row r="156">
@@ -10384,11 +9992,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L157" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L157" s="15" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
     </row>
     <row r="158">
@@ -10439,11 +10043,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L158" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L158" s="15" t="inlineStr"/>
       <c r="M158" t="inlineStr"/>
     </row>
     <row r="159">
@@ -10494,11 +10094,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L159" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L159" s="15" t="inlineStr"/>
       <c r="M159" t="inlineStr"/>
     </row>
     <row r="160">
@@ -10549,11 +10145,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L160" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L160" s="15" t="inlineStr"/>
       <c r="M160" t="inlineStr"/>
     </row>
     <row r="161">
@@ -10604,11 +10196,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L161" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L161" s="15" t="inlineStr"/>
       <c r="M161" t="inlineStr"/>
     </row>
     <row r="162">
@@ -10659,11 +10247,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L162" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L162" s="15" t="inlineStr"/>
       <c r="M162" t="inlineStr"/>
     </row>
     <row r="163">
@@ -10714,11 +10298,7 @@
           <t>生物、物理、化学</t>
         </is>
       </c>
-      <c r="L163" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L163" s="15" t="inlineStr"/>
       <c r="M163" t="inlineStr"/>
     </row>
     <row r="164">
@@ -10755,11 +10335,7 @@
           <t>生物、物理、化学</t>
         </is>
       </c>
-      <c r="L164" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L164" s="15" t="inlineStr"/>
       <c r="M164" t="inlineStr"/>
     </row>
     <row r="165">
@@ -10865,11 +10441,7 @@
           <t>综合能力测试</t>
         </is>
       </c>
-      <c r="L166" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L166" s="15" t="inlineStr"/>
       <c r="M166" t="inlineStr"/>
     </row>
     <row r="167">
@@ -10920,11 +10492,7 @@
           <t>综合能力测试</t>
         </is>
       </c>
-      <c r="L167" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L167" s="15" t="inlineStr"/>
       <c r="M167" t="inlineStr"/>
     </row>
     <row r="168">
@@ -10975,11 +10543,7 @@
           <t>综合能力测试</t>
         </is>
       </c>
-      <c r="L168" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L168" s="15" t="inlineStr"/>
       <c r="M168" t="inlineStr"/>
     </row>
     <row r="169">
@@ -11030,11 +10594,7 @@
           <t>综合能力测试</t>
         </is>
       </c>
-      <c r="L169" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L169" s="15" t="inlineStr"/>
       <c r="M169" t="inlineStr"/>
     </row>
     <row r="170">
@@ -11085,11 +10645,7 @@
           <t>综合能力测试</t>
         </is>
       </c>
-      <c r="L170" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L170" s="15" t="inlineStr"/>
       <c r="M170" t="inlineStr"/>
     </row>
     <row r="171">
@@ -11140,11 +10696,7 @@
           <t>综合能力测试</t>
         </is>
       </c>
-      <c r="L171" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L171" s="15" t="inlineStr"/>
       <c r="M171" t="inlineStr"/>
     </row>
     <row r="172">
@@ -11195,11 +10747,7 @@
           <t>中国通史和世界通史</t>
         </is>
       </c>
-      <c r="L172" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L172" s="15" t="inlineStr"/>
       <c r="M172" t="inlineStr"/>
     </row>
     <row r="173">
@@ -11250,11 +10798,7 @@
           <t>马克思主义哲学、中国哲学、外国哲学</t>
         </is>
       </c>
-      <c r="L173" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L173" s="15" t="inlineStr"/>
       <c r="M173" t="inlineStr"/>
     </row>
     <row r="174">
@@ -11346,11 +10890,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L175" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L175" s="15" t="inlineStr"/>
       <c r="M175" t="inlineStr"/>
     </row>
     <row r="176">
@@ -11401,11 +10941,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L176" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L176" s="15" t="inlineStr"/>
       <c r="M176" t="inlineStr"/>
     </row>
     <row r="177">
@@ -11456,11 +10992,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L177" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L177" s="15" t="inlineStr"/>
       <c r="M177" t="inlineStr"/>
     </row>
     <row r="178">
@@ -11511,11 +11043,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L178" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L178" s="15" t="inlineStr"/>
       <c r="M178" t="inlineStr"/>
     </row>
     <row r="179">
@@ -11566,11 +11094,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L179" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L179" s="15" t="inlineStr"/>
       <c r="M179" t="inlineStr"/>
     </row>
     <row r="180">
@@ -11607,11 +11131,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L180" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L180" s="15" t="inlineStr"/>
       <c r="M180" t="inlineStr"/>
     </row>
     <row r="181">
@@ -11648,11 +11168,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L181" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L181" s="15" t="inlineStr"/>
       <c r="M181" t="inlineStr"/>
     </row>
     <row r="182">
@@ -11758,11 +11274,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L183" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L183" s="15" t="inlineStr"/>
       <c r="M183" t="inlineStr"/>
     </row>
     <row r="184">
@@ -11813,11 +11325,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L184" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L184" s="15" t="inlineStr"/>
       <c r="M184" t="inlineStr"/>
     </row>
     <row r="185">
@@ -11868,11 +11376,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L185" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L185" s="15" t="inlineStr"/>
       <c r="M185" t="inlineStr"/>
     </row>
     <row r="186">
@@ -11923,11 +11427,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L186" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L186" s="15" t="inlineStr"/>
       <c r="M186" t="inlineStr"/>
     </row>
     <row r="187">
@@ -11978,11 +11478,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L187" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L187" s="15" t="inlineStr"/>
       <c r="M187" t="inlineStr"/>
     </row>
     <row r="188">
@@ -12033,11 +11529,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L188" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L188" s="15" t="inlineStr"/>
       <c r="M188" t="inlineStr"/>
     </row>
     <row r="189">
@@ -12088,11 +11580,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L189" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L189" s="15" t="inlineStr"/>
       <c r="M189" t="inlineStr"/>
     </row>
     <row r="190">
@@ -12143,11 +11631,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L190" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L190" s="15" t="inlineStr"/>
       <c r="M190" t="inlineStr"/>
     </row>
     <row r="191">
@@ -12198,11 +11682,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L191" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L191" s="15" t="inlineStr"/>
       <c r="M191" t="inlineStr"/>
     </row>
     <row r="192">
@@ -12253,11 +11733,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L192" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L192" s="15" t="inlineStr"/>
       <c r="M192" t="inlineStr"/>
     </row>
     <row r="193">
@@ -12294,11 +11770,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L193" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L193" s="15" t="inlineStr"/>
       <c r="M193" t="inlineStr"/>
     </row>
     <row r="194">
@@ -12335,11 +11807,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L194" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L194" s="15" t="inlineStr"/>
       <c r="M194" t="inlineStr"/>
     </row>
     <row r="195">
@@ -12376,11 +11844,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L195" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L195" s="15" t="inlineStr"/>
       <c r="M195" t="inlineStr"/>
     </row>
     <row r="196">
@@ -12417,11 +11881,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L196" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L196" s="15" t="inlineStr"/>
       <c r="M196" t="inlineStr"/>
     </row>
     <row r="197">
@@ -12472,11 +11932,7 @@
           <t>学科潜质、创新能力、科研志向</t>
         </is>
       </c>
-      <c r="L197" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L197" s="15" t="inlineStr"/>
       <c r="M197" t="inlineStr"/>
     </row>
     <row r="198">
@@ -12527,11 +11983,7 @@
           <t>数学</t>
         </is>
       </c>
-      <c r="L198" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L198" s="15" t="inlineStr"/>
       <c r="M198" t="inlineStr"/>
     </row>
     <row r="199">
@@ -12582,11 +12034,7 @@
           <t>物理</t>
         </is>
       </c>
-      <c r="L199" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L199" s="15" t="inlineStr"/>
       <c r="M199" t="inlineStr"/>
     </row>
     <row r="200">
@@ -12637,11 +12085,7 @@
           <t>化学</t>
         </is>
       </c>
-      <c r="L200" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L200" s="15" t="inlineStr"/>
       <c r="M200" t="inlineStr"/>
     </row>
     <row r="201">
@@ -12690,11 +12134,7 @@
           <t>语文</t>
         </is>
       </c>
-      <c r="L201" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L201" s="15" t="inlineStr"/>
       <c r="M201" t="inlineStr"/>
     </row>
     <row r="202">
@@ -12745,11 +12185,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L202" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L202" s="15" t="inlineStr"/>
       <c r="M202" t="inlineStr"/>
     </row>
     <row r="203">
@@ -12800,11 +12236,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L203" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L203" s="15" t="inlineStr"/>
       <c r="M203" t="inlineStr"/>
     </row>
     <row r="204">
@@ -12965,11 +12397,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L206" s="15" t="inlineStr">
-        <is>
-          <t>航天材料</t>
-        </is>
-      </c>
+      <c r="L206" s="15" t="inlineStr"/>
       <c r="M206" t="inlineStr"/>
     </row>
     <row r="207">
@@ -13020,11 +12448,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L207" s="15" t="inlineStr">
-        <is>
-          <t>航天材料</t>
-        </is>
-      </c>
+      <c r="L207" s="15" t="inlineStr"/>
       <c r="M207" t="inlineStr"/>
     </row>
     <row r="208">
@@ -13075,11 +12499,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L208" s="15" t="inlineStr">
-        <is>
-          <t>航天材料</t>
-        </is>
-      </c>
+      <c r="L208" s="15" t="inlineStr"/>
       <c r="M208" t="inlineStr"/>
     </row>
     <row r="209">
@@ -13130,11 +12550,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L209" s="15" t="inlineStr">
-        <is>
-          <t>航天材料</t>
-        </is>
-      </c>
+      <c r="L209" s="15" t="inlineStr"/>
       <c r="M209" t="inlineStr"/>
     </row>
     <row r="210">
@@ -13225,11 +12641,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L211" s="15" t="inlineStr">
-        <is>
-          <t>航天材料</t>
-        </is>
-      </c>
+      <c r="L211" s="15" t="inlineStr"/>
       <c r="M211" t="inlineStr"/>
     </row>
     <row r="212">
@@ -13280,11 +12692,7 @@
           <t>数学</t>
         </is>
       </c>
-      <c r="L212" s="15" t="inlineStr">
-        <is>
-          <t>航天材料</t>
-        </is>
-      </c>
+      <c r="L212" s="15" t="inlineStr"/>
       <c r="M212" t="inlineStr"/>
     </row>
     <row r="213">
@@ -13335,11 +12743,7 @@
           <t>数学</t>
         </is>
       </c>
-      <c r="L213" s="15" t="inlineStr">
-        <is>
-          <t>航天材料</t>
-        </is>
-      </c>
+      <c r="L213" s="15" t="inlineStr"/>
       <c r="M213" t="inlineStr"/>
     </row>
     <row r="214">
@@ -13376,11 +12780,7 @@
           <t>数学</t>
         </is>
       </c>
-      <c r="L214" s="15" t="inlineStr">
-        <is>
-          <t>航天材料</t>
-        </is>
-      </c>
+      <c r="L214" s="15" t="inlineStr"/>
       <c r="M214" t="inlineStr"/>
     </row>
     <row r="215">
@@ -13417,11 +12817,7 @@
           <t>文科综合</t>
         </is>
       </c>
-      <c r="L215" s="15" t="inlineStr">
-        <is>
-          <t>航天材料</t>
-        </is>
-      </c>
+      <c r="L215" s="15" t="inlineStr"/>
       <c r="M215" t="inlineStr"/>
     </row>
     <row r="216">
@@ -13527,11 +12923,7 @@
           <t>相关学科基础</t>
         </is>
       </c>
-      <c r="L217" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L217" s="15" t="inlineStr"/>
       <c r="M217" t="inlineStr"/>
     </row>
     <row r="218">
@@ -13582,11 +12974,7 @@
           <t>相关学科基础</t>
         </is>
       </c>
-      <c r="L218" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L218" s="15" t="inlineStr"/>
       <c r="M218" t="inlineStr"/>
     </row>
     <row r="219">
@@ -13637,11 +13025,7 @@
           <t>相关学科基础</t>
         </is>
       </c>
-      <c r="L219" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L219" s="15" t="inlineStr"/>
       <c r="M219" t="inlineStr"/>
     </row>
     <row r="220">
@@ -13692,11 +13076,7 @@
           <t>相关学科基础</t>
         </is>
       </c>
-      <c r="L220" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L220" s="15" t="inlineStr"/>
       <c r="M220" t="inlineStr"/>
     </row>
     <row r="221">
@@ -13747,11 +13127,7 @@
           <t>相关学科基础</t>
         </is>
       </c>
-      <c r="L221" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L221" s="15" t="inlineStr"/>
       <c r="M221" t="inlineStr"/>
     </row>
     <row r="222">
@@ -13788,11 +13164,7 @@
           <t>相关学科基础</t>
         </is>
       </c>
-      <c r="L222" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
+      <c r="L222" s="15" t="inlineStr"/>
       <c r="M222" t="inlineStr"/>
     </row>
     <row r="223">
@@ -13898,11 +13270,7 @@
           <t>相关学科基础</t>
         </is>
       </c>
-      <c r="L224" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L224" s="15" t="inlineStr"/>
       <c r="M224" t="inlineStr"/>
     </row>
     <row r="225">
@@ -13953,11 +13321,7 @@
           <t>相关学科基础</t>
         </is>
       </c>
-      <c r="L225" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L225" s="15" t="inlineStr"/>
       <c r="M225" t="inlineStr"/>
     </row>
     <row r="226">
@@ -14008,11 +13372,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L226" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L226" s="15" t="inlineStr"/>
       <c r="M226" t="inlineStr"/>
     </row>
     <row r="227">
@@ -14063,11 +13423,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L227" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L227" s="15" t="inlineStr"/>
       <c r="M227" t="inlineStr"/>
     </row>
     <row r="228">
@@ -14118,11 +13474,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L228" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L228" s="15" t="inlineStr"/>
       <c r="M228" t="inlineStr"/>
     </row>
     <row r="229">
@@ -14173,11 +13525,7 @@
           <t>相关学科的基础知识</t>
         </is>
       </c>
-      <c r="L229" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L229" s="15" t="inlineStr"/>
       <c r="M229" t="inlineStr"/>
     </row>
     <row r="230">
@@ -14283,11 +13631,7 @@
           <t>相关学科的基础知识</t>
         </is>
       </c>
-      <c r="L231" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L231" s="15" t="inlineStr"/>
       <c r="M231" t="inlineStr"/>
     </row>
     <row r="232">
@@ -14338,11 +13682,7 @@
           <t>相关学科的基础知识</t>
         </is>
       </c>
-      <c r="L232" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L232" s="15" t="inlineStr"/>
       <c r="M232" t="inlineStr"/>
     </row>
     <row r="233">
@@ -14393,11 +13733,7 @@
           <t>相关学科的基础知识</t>
         </is>
       </c>
-      <c r="L233" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L233" s="15" t="inlineStr"/>
       <c r="M233" t="inlineStr"/>
     </row>
     <row r="234">
@@ -14448,11 +13784,7 @@
           <t>相关学科的基础知识</t>
         </is>
       </c>
-      <c r="L234" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L234" s="15" t="inlineStr"/>
       <c r="M234" t="inlineStr"/>
     </row>
     <row r="235">
@@ -14503,11 +13835,7 @@
           <t>相关学科的基础知识</t>
         </is>
       </c>
-      <c r="L235" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L235" s="15" t="inlineStr"/>
       <c r="M235" t="inlineStr"/>
     </row>
     <row r="236">
@@ -14544,11 +13872,7 @@
           <t>相关学科的基础知识</t>
         </is>
       </c>
-      <c r="L236" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L236" s="15" t="inlineStr"/>
       <c r="M236" t="inlineStr"/>
     </row>
     <row r="237">
@@ -14599,11 +13923,7 @@
           <t>相关学科的基础知识</t>
         </is>
       </c>
-      <c r="L237" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L237" s="15" t="inlineStr"/>
       <c r="M237" t="inlineStr"/>
     </row>
     <row r="238">
@@ -14654,11 +13974,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L238" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L238" s="15" t="inlineStr"/>
       <c r="M238" t="inlineStr"/>
     </row>
     <row r="239">
@@ -14709,11 +14025,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L239" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L239" s="15" t="inlineStr"/>
       <c r="M239" t="inlineStr"/>
     </row>
     <row r="240">
@@ -14750,11 +14062,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L240" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L240" s="15" t="inlineStr"/>
       <c r="M240" t="inlineStr"/>
     </row>
     <row r="241">
@@ -14805,11 +14113,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L241" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L241" s="15" t="inlineStr"/>
       <c r="M241" t="inlineStr"/>
     </row>
     <row r="242">
@@ -14846,11 +14150,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L242" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L242" s="15" t="inlineStr"/>
       <c r="M242" t="inlineStr"/>
     </row>
     <row r="243">
@@ -14928,11 +14228,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L244" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L244" s="15" t="inlineStr"/>
       <c r="M244" t="inlineStr"/>
     </row>
     <row r="245">
@@ -14983,11 +14279,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L245" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L245" s="15" t="inlineStr"/>
       <c r="M245" t="inlineStr"/>
     </row>
     <row r="246">
@@ -15038,11 +14330,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L246" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L246" s="15" t="inlineStr"/>
       <c r="M246" t="inlineStr"/>
     </row>
     <row r="247">
@@ -15093,11 +14381,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L247" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L247" s="15" t="inlineStr"/>
       <c r="M247" t="inlineStr"/>
     </row>
     <row r="248">
@@ -15148,11 +14432,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L248" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L248" s="15" t="inlineStr"/>
       <c r="M248" t="inlineStr"/>
     </row>
     <row r="249">
@@ -15203,11 +14483,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L249" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L249" s="15" t="inlineStr"/>
       <c r="M249" t="inlineStr"/>
     </row>
     <row r="250">
@@ -15258,11 +14534,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L250" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L250" s="15" t="inlineStr"/>
       <c r="M250" t="inlineStr"/>
     </row>
     <row r="251">
@@ -15368,11 +14640,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L252" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L252" s="15" t="inlineStr"/>
       <c r="M252" t="inlineStr"/>
     </row>
     <row r="253">
@@ -15409,11 +14677,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L253" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L253" s="15" t="inlineStr"/>
       <c r="M253" t="inlineStr"/>
     </row>
     <row r="254">
@@ -15464,11 +14728,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L254" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L254" s="15" t="inlineStr"/>
       <c r="M254" t="inlineStr"/>
     </row>
     <row r="255">
@@ -15519,11 +14779,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L255" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L255" s="15" t="inlineStr"/>
       <c r="M255" t="inlineStr"/>
     </row>
     <row r="256">
@@ -15574,11 +14830,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L256" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L256" s="15" t="inlineStr"/>
       <c r="M256" t="inlineStr"/>
     </row>
     <row r="257">
@@ -15615,11 +14867,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L257" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L257" s="15" t="inlineStr"/>
       <c r="M257" t="inlineStr"/>
     </row>
     <row r="258">
@@ -15656,11 +14904,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L258" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L258" s="15" t="inlineStr"/>
       <c r="M258" t="inlineStr"/>
     </row>
     <row r="259">
@@ -15697,11 +14941,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L259" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L259" s="15" t="inlineStr"/>
       <c r="M259" t="inlineStr"/>
     </row>
     <row r="260">
@@ -15738,11 +14978,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L260" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L260" s="15" t="inlineStr"/>
       <c r="M260" t="inlineStr"/>
     </row>
     <row r="261">
@@ -15834,11 +15070,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L262" s="15" t="inlineStr">
-        <is>
-          <t>生物医药</t>
-        </is>
-      </c>
+      <c r="L262" s="15" t="inlineStr"/>
       <c r="M262" t="inlineStr"/>
     </row>
     <row r="263">
@@ -15969,11 +15201,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L265" s="15" t="inlineStr">
-        <is>
-          <t>生物医药</t>
-        </is>
-      </c>
+      <c r="L265" s="15" t="inlineStr"/>
       <c r="M265" t="inlineStr"/>
     </row>
     <row r="266">
@@ -16024,11 +15252,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L266" s="15" t="inlineStr">
-        <is>
-          <t>生物医药</t>
-        </is>
-      </c>
+      <c r="L266" s="15" t="inlineStr"/>
       <c r="M266" t="inlineStr"/>
     </row>
     <row r="267">
@@ -16079,11 +15303,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L267" s="15" t="inlineStr">
-        <is>
-          <t>生物医药</t>
-        </is>
-      </c>
+      <c r="L267" s="15" t="inlineStr"/>
       <c r="M267" t="inlineStr"/>
     </row>
     <row r="268">
@@ -16189,11 +15409,7 @@
           <t>语文、历史</t>
         </is>
       </c>
-      <c r="L269" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L269" s="15" t="inlineStr"/>
       <c r="M269" t="inlineStr"/>
     </row>
     <row r="270">
@@ -16244,11 +15460,7 @@
           <t>语文、历史</t>
         </is>
       </c>
-      <c r="L270" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L270" s="15" t="inlineStr"/>
       <c r="M270" t="inlineStr"/>
     </row>
     <row r="271">
@@ -16299,11 +15511,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L271" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L271" s="15" t="inlineStr"/>
       <c r="M271" t="inlineStr"/>
     </row>
     <row r="272">
@@ -16354,11 +15562,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L272" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L272" s="15" t="inlineStr"/>
       <c r="M272" t="inlineStr"/>
     </row>
     <row r="273">
@@ -16409,11 +15613,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L273" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L273" s="15" t="inlineStr"/>
       <c r="M273" t="inlineStr"/>
     </row>
     <row r="274">
@@ -16464,11 +15664,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L274" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L274" s="15" t="inlineStr"/>
       <c r="M274" t="inlineStr"/>
     </row>
     <row r="275">
@@ -16519,11 +15715,7 @@
           <t>化学、生物</t>
         </is>
       </c>
-      <c r="L275" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L275" s="15" t="inlineStr"/>
       <c r="M275" t="inlineStr"/>
     </row>
     <row r="276">
@@ -16574,11 +15766,7 @@
           <t>化学、生物</t>
         </is>
       </c>
-      <c r="L276" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L276" s="15" t="inlineStr"/>
       <c r="M276" t="inlineStr"/>
     </row>
     <row r="277">
@@ -16629,11 +15817,7 @@
           <t>化学、生物</t>
         </is>
       </c>
-      <c r="L277" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L277" s="15" t="inlineStr"/>
       <c r="M277" t="inlineStr"/>
     </row>
     <row r="278">
@@ -16684,11 +15868,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L278" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L278" s="15" t="inlineStr"/>
       <c r="M278" t="inlineStr"/>
     </row>
     <row r="279">
@@ -16739,11 +15919,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L279" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L279" s="15" t="inlineStr"/>
       <c r="M279" t="inlineStr"/>
     </row>
     <row r="280">
@@ -16794,11 +15970,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L280" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L280" s="15" t="inlineStr"/>
       <c r="M280" t="inlineStr"/>
     </row>
     <row r="281">
@@ -16849,11 +16021,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L281" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L281" s="15" t="inlineStr"/>
       <c r="M281" t="inlineStr"/>
     </row>
     <row r="282">
@@ -16904,11 +16072,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L282" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L282" s="15" t="inlineStr"/>
       <c r="M282" t="inlineStr"/>
     </row>
     <row r="283">
@@ -16959,11 +16123,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L283" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L283" s="15" t="inlineStr"/>
       <c r="M283" t="inlineStr"/>
     </row>
     <row r="284">
@@ -17014,11 +16174,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L284" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L284" s="15" t="inlineStr"/>
       <c r="M284" t="inlineStr"/>
     </row>
     <row r="285">
@@ -17069,11 +16225,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L285" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L285" s="15" t="inlineStr"/>
       <c r="M285" t="inlineStr"/>
     </row>
     <row r="286">
@@ -17110,11 +16262,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L286" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L286" s="15" t="inlineStr"/>
       <c r="M286" t="inlineStr"/>
     </row>
     <row r="287">
@@ -17177,11 +16325,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L288" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L288" s="15" t="inlineStr"/>
       <c r="M288" t="inlineStr"/>
     </row>
     <row r="289">
@@ -17218,11 +16362,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L289" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L289" s="15" t="inlineStr"/>
       <c r="M289" t="inlineStr"/>
     </row>
     <row r="290">
@@ -17259,11 +16399,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L290" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L290" s="15" t="inlineStr"/>
       <c r="M290" t="inlineStr"/>
     </row>
     <row r="291">
@@ -17314,11 +16450,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L291" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L291" s="15" t="inlineStr"/>
       <c r="M291" t="inlineStr"/>
     </row>
     <row r="292">
@@ -17369,11 +16501,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L292" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L292" s="15" t="inlineStr"/>
       <c r="M292" t="inlineStr"/>
     </row>
     <row r="293">
@@ -17424,11 +16552,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L293" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L293" s="15" t="inlineStr"/>
       <c r="M293" t="inlineStr"/>
     </row>
     <row r="294">
@@ -17479,11 +16603,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L294" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
+      <c r="L294" s="15" t="inlineStr"/>
       <c r="M294" t="inlineStr"/>
     </row>
     <row r="295">
@@ -17561,11 +16681,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L296" s="15" t="inlineStr">
-        <is>
-          <t>草类植物生物育种</t>
-        </is>
-      </c>
+      <c r="L296" s="15" t="inlineStr"/>
       <c r="M296" t="inlineStr"/>
     </row>
     <row r="297">
@@ -17616,11 +16732,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L297" s="15" t="inlineStr">
-        <is>
-          <t>草类植物生物育种</t>
-        </is>
-      </c>
+      <c r="L297" s="15" t="inlineStr"/>
       <c r="M297" t="inlineStr"/>
     </row>
     <row r="298">
@@ -17671,11 +16783,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L298" s="15" t="inlineStr">
-        <is>
-          <t>草类植物生物育种</t>
-        </is>
-      </c>
+      <c r="L298" s="15" t="inlineStr"/>
       <c r="M298" t="inlineStr"/>
     </row>
     <row r="299">
@@ -17765,11 +16873,7 @@
           <t>数学与逻辑、经典物理</t>
         </is>
       </c>
-      <c r="L300" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L300" s="15" t="inlineStr"/>
       <c r="M300" t="inlineStr"/>
     </row>
     <row r="301">
@@ -17804,11 +16908,7 @@
           <t>数学与逻辑、经典物理</t>
         </is>
       </c>
-      <c r="L301" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L301" s="15" t="inlineStr"/>
       <c r="M301" t="inlineStr"/>
     </row>
     <row r="302">
@@ -17857,11 +16957,7 @@
           <t>数学与逻辑、经典物理</t>
         </is>
       </c>
-      <c r="L302" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L302" s="15" t="inlineStr"/>
       <c r="M302" t="inlineStr"/>
     </row>
     <row r="303">
@@ -17912,11 +17008,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L303" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L303" s="15" t="inlineStr"/>
       <c r="M303" t="inlineStr"/>
     </row>
     <row r="304">
@@ -17967,11 +17059,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L304" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L304" s="15" t="inlineStr"/>
       <c r="M304" t="inlineStr"/>
     </row>
     <row r="305">
@@ -18022,11 +17110,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L305" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
+      <c r="L305" s="15" t="inlineStr"/>
       <c r="M305" t="inlineStr"/>
     </row>
   </sheetData>

--- a/强基查证清单.xlsx
+++ b/强基查证清单.xlsx
@@ -2519,7 +2519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M305"/>
+  <dimension ref="A1:L305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2534,7 +2534,6 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2595,11 +2594,6 @@
       </c>
       <c r="L1" s="14" t="inlineStr">
         <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="M1" s="14" t="inlineStr">
-        <is>
           <t>校验</t>
         </is>
       </c>
@@ -2652,8 +2646,7 @@
           <t>数学</t>
         </is>
       </c>
-      <c r="L2" s="15" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2703,8 +2696,7 @@
           <t>数学、计算科学</t>
         </is>
       </c>
-      <c r="L3" s="15" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2754,8 +2746,7 @@
           <t>物理</t>
         </is>
       </c>
-      <c r="L4" s="15" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2805,8 +2796,7 @@
           <t>化学</t>
         </is>
       </c>
-      <c r="L5" s="15" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2856,8 +2846,7 @@
           <t>数理化综合</t>
         </is>
       </c>
-      <c r="L6" s="15" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2907,8 +2896,7 @@
           <t>数理化综合</t>
         </is>
       </c>
-      <c r="L7" s="15" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2956,12 +2944,7 @@
           <t>文史哲综合</t>
         </is>
       </c>
-      <c r="L8" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3011,8 +2994,7 @@
           <t>文史哲综合</t>
         </is>
       </c>
-      <c r="L9" s="15" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3062,8 +3044,7 @@
           <t>文史哲综合</t>
         </is>
       </c>
-      <c r="L10" s="15" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -3113,8 +3094,7 @@
           <t>数学+物理</t>
         </is>
       </c>
-      <c r="L11" s="15" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -3164,8 +3144,7 @@
           <t>数学+物理</t>
         </is>
       </c>
-      <c r="L12" s="15" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -3215,8 +3194,7 @@
           <t>数学+物理</t>
         </is>
       </c>
-      <c r="L13" s="15" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3266,8 +3244,7 @@
           <t>数学+物理</t>
         </is>
       </c>
-      <c r="L14" s="15" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -3317,8 +3294,7 @@
           <t>数学+物理</t>
         </is>
       </c>
-      <c r="L15" s="15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3368,8 +3344,7 @@
           <t>数学+物理</t>
         </is>
       </c>
-      <c r="L16" s="15" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3419,8 +3394,7 @@
           <t>数学+化学</t>
         </is>
       </c>
-      <c r="L17" s="15" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3470,8 +3444,7 @@
           <t>数学+化学</t>
         </is>
       </c>
-      <c r="L18" s="15" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3521,8 +3494,7 @@
           <t>数学+化学</t>
         </is>
       </c>
-      <c r="L19" s="15" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3572,8 +3544,7 @@
           <t>数理探究</t>
         </is>
       </c>
-      <c r="L20" s="15" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3623,8 +3594,7 @@
           <t>数理探究</t>
         </is>
       </c>
-      <c r="L21" s="15" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3674,8 +3644,7 @@
           <t>数理探究</t>
         </is>
       </c>
-      <c r="L22" s="15" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3725,8 +3694,7 @@
           <t>数理探究</t>
         </is>
       </c>
-      <c r="L23" s="15" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3776,8 +3744,7 @@
           <t>数理探究</t>
         </is>
       </c>
-      <c r="L24" s="15" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3813,12 +3780,7 @@
           <t>阅读表达</t>
         </is>
       </c>
-      <c r="L25" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3854,8 +3816,7 @@
           <t>阅读表达</t>
         </is>
       </c>
-      <c r="L26" s="15" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3891,8 +3852,7 @@
           <t>阅读表达</t>
         </is>
       </c>
-      <c r="L27" s="15" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3938,8 +3898,7 @@
         </is>
       </c>
       <c r="K28" s="15" t="inlineStr"/>
-      <c r="L28" s="15" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3985,8 +3944,7 @@
         </is>
       </c>
       <c r="K29" s="15" t="inlineStr"/>
-      <c r="L29" s="15" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4026,7 +3984,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4066,7 +4024,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4106,7 +4064,7 @@
           <t>大类</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4152,8 +4110,7 @@
         </is>
       </c>
       <c r="K33" s="15" t="inlineStr"/>
-      <c r="L33" s="15" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4193,7 +4150,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4239,8 +4196,7 @@
         </is>
       </c>
       <c r="K35" s="15" t="inlineStr"/>
-      <c r="L35" s="15" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4290,8 +4246,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L36" s="15" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4331,7 +4286,7 @@
           <t>试验班</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4381,8 +4336,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L38" s="15" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4422,7 +4376,7 @@
           <t>试验班</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4472,8 +4426,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L40" s="15" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4523,8 +4476,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L41" s="15" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4564,7 +4516,7 @@
           <t>试验班</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4614,8 +4566,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L43" s="15" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4665,8 +4616,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L44" s="15" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4704,7 +4654,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4754,8 +4704,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L46" s="15" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4805,8 +4754,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L47" s="15" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4856,8 +4804,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L48" s="15" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4907,8 +4854,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L49" s="15" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4958,8 +4904,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L50" s="15" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5009,8 +4954,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L51" s="15" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5060,8 +5004,7 @@
           <t>数学、化学</t>
         </is>
       </c>
-      <c r="L52" s="15" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5111,8 +5054,7 @@
           <t>数学、化学</t>
         </is>
       </c>
-      <c r="L53" s="15" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5162,8 +5104,7 @@
           <t>数学、化学</t>
         </is>
       </c>
-      <c r="L54" s="15" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5213,8 +5154,7 @@
           <t>数学、化学</t>
         </is>
       </c>
-      <c r="L55" s="15" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -5250,8 +5190,7 @@
           <t>数学、化学</t>
         </is>
       </c>
-      <c r="L56" s="15" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -5301,8 +5240,7 @@
           <t>数学、化学</t>
         </is>
       </c>
-      <c r="L57" s="15" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -5352,12 +5290,7 @@
           <t>语文、历史</t>
         </is>
       </c>
-      <c r="L58" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -5407,8 +5340,7 @@
           <t>语文、历史</t>
         </is>
       </c>
-      <c r="L59" s="15" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -5458,8 +5390,7 @@
           <t>语文、历史</t>
         </is>
       </c>
-      <c r="L60" s="15" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5509,8 +5440,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L61" s="15" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5550,7 +5480,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5600,8 +5530,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L63" s="15" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5651,8 +5580,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L64" s="15" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5702,8 +5630,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L65" s="15" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -5753,8 +5680,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L66" s="15" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5804,8 +5730,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L67" s="15" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5855,8 +5780,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L68" s="15" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5906,8 +5830,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L69" s="15" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5957,8 +5880,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L70" s="15" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -6008,8 +5930,7 @@
           <t>语文、历史</t>
         </is>
       </c>
-      <c r="L71" s="15" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -6059,8 +5980,7 @@
           <t>数理综合</t>
         </is>
       </c>
-      <c r="L72" s="15" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -6110,8 +6030,7 @@
           <t>数理综合</t>
         </is>
       </c>
-      <c r="L73" s="15" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -6161,8 +6080,7 @@
           <t>数理综合</t>
         </is>
       </c>
-      <c r="L74" s="15" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -6210,8 +6128,7 @@
           <t>数理综合</t>
         </is>
       </c>
-      <c r="L75" s="15" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -6261,8 +6178,7 @@
           <t>化学</t>
         </is>
       </c>
-      <c r="L76" s="15" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -6312,8 +6228,7 @@
           <t>化学</t>
         </is>
       </c>
-      <c r="L77" s="15" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -6363,8 +6278,7 @@
           <t>数理综合</t>
         </is>
       </c>
-      <c r="L78" s="15" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -6404,7 +6318,7 @@
           <t>大类</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -6454,8 +6368,7 @@
           <t>数理综合</t>
         </is>
       </c>
-      <c r="L80" s="15" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -6505,8 +6418,7 @@
           <t>数理化综合</t>
         </is>
       </c>
-      <c r="L81" s="15" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6546,7 +6458,7 @@
           <t>大类</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6586,7 +6498,7 @@
           <t>大类</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6626,7 +6538,7 @@
           <t>大类</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6676,8 +6588,7 @@
           <t>数理化综合</t>
         </is>
       </c>
-      <c r="L85" s="15" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6717,7 +6628,7 @@
           <t>试验班</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6757,7 +6668,7 @@
           <t>试验班</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6807,8 +6718,7 @@
           <t>数理化综合</t>
         </is>
       </c>
-      <c r="L88" s="15" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6858,8 +6768,7 @@
           <t>数理化综合</t>
         </is>
       </c>
-      <c r="L89" s="15" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -6909,8 +6818,7 @@
           <t>文史哲综合</t>
         </is>
       </c>
-      <c r="L90" s="15" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6960,8 +6868,7 @@
           <t>文史哲综合</t>
         </is>
       </c>
-      <c r="L91" s="15" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -7011,8 +6918,7 @@
           <t>数学及航空航天知识基础、数学拔高</t>
         </is>
       </c>
-      <c r="L92" s="15" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -7062,8 +6968,7 @@
           <t>数学及航空航天知识基础、化学拔高</t>
         </is>
       </c>
-      <c r="L93" s="15" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -7113,8 +7018,7 @@
           <t>数学及航空航天知识基础、物理拔高</t>
         </is>
       </c>
-      <c r="L94" s="15" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -7164,8 +7068,7 @@
           <t>数学及航空航天知识基础、物理拔高</t>
         </is>
       </c>
-      <c r="L95" s="15" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7215,8 +7118,7 @@
           <t>数学及航空航天知识基础、物理拔高</t>
         </is>
       </c>
-      <c r="L96" s="15" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7266,12 +7168,7 @@
           <t>数学及航空航天知识基础、物理拔高</t>
         </is>
       </c>
-      <c r="L97" s="15" t="inlineStr">
-        <is>
-          <t>量子信息</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7321,8 +7218,7 @@
           <t>数学及航空航天知识基础、物理拔高</t>
         </is>
       </c>
-      <c r="L98" s="15" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7372,8 +7268,7 @@
           <t>数学及航空航天知识基础、物理拔高</t>
         </is>
       </c>
-      <c r="L99" s="15" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -7413,7 +7308,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7453,7 +7348,7 @@
           <t>试验班</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -7503,8 +7398,7 @@
           <t>数理科技相关</t>
         </is>
       </c>
-      <c r="L102" s="15" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -7554,12 +7448,7 @@
           <t>文史哲相关</t>
         </is>
       </c>
-      <c r="L103" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -7609,8 +7498,7 @@
           <t>文史哲相关</t>
         </is>
       </c>
-      <c r="L104" s="15" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -7650,7 +7538,7 @@
           <t>试验班</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -7700,8 +7588,7 @@
           <t>文史哲相关</t>
         </is>
       </c>
-      <c r="L106" s="15" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -7751,8 +7638,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L107" s="15" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -7802,8 +7688,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L108" s="15" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -7853,8 +7738,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L109" s="15" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -7904,8 +7788,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L110" s="15" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -7955,8 +7838,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L111" s="15" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -8006,8 +7888,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L112" s="15" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -8047,7 +7928,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -8087,7 +7968,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -8127,7 +8008,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -8167,7 +8048,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -8207,7 +8088,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -8247,7 +8128,7 @@
           <t>同专业类</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -8287,7 +8168,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -8327,7 +8208,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -8367,7 +8248,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -8405,7 +8286,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -8445,7 +8326,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -8495,8 +8376,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L124" s="15" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -8546,8 +8426,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L125" s="15" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -8597,12 +8476,7 @@
           <t>数学、语文、历史</t>
         </is>
       </c>
-      <c r="L126" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -8642,7 +8516,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -8692,8 +8566,7 @@
           <t>数学、语文、历史</t>
         </is>
       </c>
-      <c r="L128" s="15" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -8743,8 +8616,7 @@
           <t>数学、语文、历史</t>
         </is>
       </c>
-      <c r="L129" s="15" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -8794,8 +8666,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L130" s="15" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8835,7 +8706,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -8875,7 +8746,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -8915,7 +8786,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -8955,7 +8826,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -9005,8 +8876,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L135" s="15" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -9046,7 +8916,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -9086,7 +8956,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -9126,7 +8996,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -9176,8 +9046,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L139" s="15" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -9217,7 +9086,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -9257,7 +9126,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -9297,7 +9166,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -9337,7 +9206,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -9377,7 +9246,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -9417,7 +9286,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -9457,7 +9326,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -9507,8 +9376,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L147" s="15" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -9558,8 +9426,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L148" s="15" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -9599,7 +9466,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -9639,7 +9506,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -9679,7 +9546,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -9729,12 +9596,7 @@
           <t>数学、物理、化学</t>
         </is>
       </c>
-      <c r="L152" s="15" t="inlineStr">
-        <is>
-          <t>八年制</t>
-        </is>
-      </c>
-      <c r="M152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -9784,8 +9646,7 @@
           <t>语文、英语、历史</t>
         </is>
       </c>
-      <c r="L153" s="15" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -9835,8 +9696,7 @@
           <t>语文、英语、历史</t>
         </is>
       </c>
-      <c r="L154" s="15" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -9886,8 +9746,7 @@
           <t>语文、英语、历史</t>
         </is>
       </c>
-      <c r="L155" s="15" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -9937,12 +9796,7 @@
           <t>语文、英语、历史</t>
         </is>
       </c>
-      <c r="L156" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
-      <c r="M156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -9992,8 +9846,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L157" s="15" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -10043,8 +9896,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L158" s="15" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -10094,8 +9946,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L159" s="15" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -10145,8 +9996,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L160" s="15" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -10196,8 +10046,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L161" s="15" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -10247,8 +10096,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L162" s="15" t="inlineStr"/>
-      <c r="M162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -10298,8 +10146,7 @@
           <t>生物、物理、化学</t>
         </is>
       </c>
-      <c r="L163" s="15" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -10335,8 +10182,7 @@
           <t>生物、物理、化学</t>
         </is>
       </c>
-      <c r="L164" s="15" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -10386,12 +10232,7 @@
           <t>综合能力测试</t>
         </is>
       </c>
-      <c r="L165" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
-      <c r="M165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -10441,8 +10282,7 @@
           <t>综合能力测试</t>
         </is>
       </c>
-      <c r="L166" s="15" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -10492,8 +10332,7 @@
           <t>综合能力测试</t>
         </is>
       </c>
-      <c r="L167" s="15" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -10543,8 +10382,7 @@
           <t>综合能力测试</t>
         </is>
       </c>
-      <c r="L168" s="15" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -10594,8 +10432,7 @@
           <t>综合能力测试</t>
         </is>
       </c>
-      <c r="L169" s="15" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -10645,8 +10482,7 @@
           <t>综合能力测试</t>
         </is>
       </c>
-      <c r="L170" s="15" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -10696,8 +10532,7 @@
           <t>综合能力测试</t>
         </is>
       </c>
-      <c r="L171" s="15" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -10747,8 +10582,7 @@
           <t>中国通史和世界通史</t>
         </is>
       </c>
-      <c r="L172" s="15" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -10798,8 +10632,7 @@
           <t>马克思主义哲学、中国哲学、外国哲学</t>
         </is>
       </c>
-      <c r="L173" s="15" t="inlineStr"/>
-      <c r="M173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -10835,12 +10668,7 @@
           <t>古代汉语、中国通史</t>
         </is>
       </c>
-      <c r="L174" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
-      <c r="M174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -10890,8 +10718,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L175" s="15" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -10941,8 +10768,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L176" s="15" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -10992,8 +10818,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L177" s="15" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -11043,8 +10868,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L178" s="15" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -11094,8 +10918,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L179" s="15" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -11131,8 +10954,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L180" s="15" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -11168,8 +10990,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L181" s="15" t="inlineStr"/>
-      <c r="M181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -11219,12 +11040,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L182" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
-      <c r="M182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -11274,8 +11090,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L183" s="15" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -11325,8 +11140,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L184" s="15" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -11376,8 +11190,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L185" s="15" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -11427,8 +11240,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L186" s="15" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -11478,8 +11290,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L187" s="15" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -11529,8 +11340,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L188" s="15" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -11580,8 +11390,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L189" s="15" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -11631,8 +11440,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L190" s="15" t="inlineStr"/>
-      <c r="M190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -11682,8 +11490,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L191" s="15" t="inlineStr"/>
-      <c r="M191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -11733,8 +11540,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L192" s="15" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -11770,8 +11576,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L193" s="15" t="inlineStr"/>
-      <c r="M193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -11807,8 +11612,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L194" s="15" t="inlineStr"/>
-      <c r="M194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -11844,8 +11648,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L195" s="15" t="inlineStr"/>
-      <c r="M195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -11881,8 +11684,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L196" s="15" t="inlineStr"/>
-      <c r="M196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -11932,8 +11734,7 @@
           <t>学科潜质、创新能力、科研志向</t>
         </is>
       </c>
-      <c r="L197" s="15" t="inlineStr"/>
-      <c r="M197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -11983,8 +11784,7 @@
           <t>数学</t>
         </is>
       </c>
-      <c r="L198" s="15" t="inlineStr"/>
-      <c r="M198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -12034,8 +11834,7 @@
           <t>物理</t>
         </is>
       </c>
-      <c r="L199" s="15" t="inlineStr"/>
-      <c r="M199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -12085,8 +11884,7 @@
           <t>化学</t>
         </is>
       </c>
-      <c r="L200" s="15" t="inlineStr"/>
-      <c r="M200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -12134,8 +11932,7 @@
           <t>语文</t>
         </is>
       </c>
-      <c r="L201" s="15" t="inlineStr"/>
-      <c r="M201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -12185,8 +11982,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L202" s="15" t="inlineStr"/>
-      <c r="M202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -12236,8 +12032,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L203" s="15" t="inlineStr"/>
-      <c r="M203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -12287,12 +12082,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L204" s="15" t="inlineStr">
-        <is>
-          <t>航天材料</t>
-        </is>
-      </c>
-      <c r="M204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -12342,12 +12132,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L205" s="15" t="inlineStr">
-        <is>
-          <t>航天材料</t>
-        </is>
-      </c>
-      <c r="M205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -12397,8 +12182,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L206" s="15" t="inlineStr"/>
-      <c r="M206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -12448,8 +12232,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L207" s="15" t="inlineStr"/>
-      <c r="M207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -12499,8 +12282,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L208" s="15" t="inlineStr"/>
-      <c r="M208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -12550,8 +12332,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L209" s="15" t="inlineStr"/>
-      <c r="M209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -12591,7 +12372,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -12641,8 +12422,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L211" s="15" t="inlineStr"/>
-      <c r="M211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -12692,8 +12472,7 @@
           <t>数学</t>
         </is>
       </c>
-      <c r="L212" s="15" t="inlineStr"/>
-      <c r="M212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -12743,8 +12522,7 @@
           <t>数学</t>
         </is>
       </c>
-      <c r="L213" s="15" t="inlineStr"/>
-      <c r="M213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -12780,8 +12558,7 @@
           <t>数学</t>
         </is>
       </c>
-      <c r="L214" s="15" t="inlineStr"/>
-      <c r="M214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -12817,8 +12594,7 @@
           <t>文科综合</t>
         </is>
       </c>
-      <c r="L215" s="15" t="inlineStr"/>
-      <c r="M215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -12868,12 +12644,7 @@
           <t>文科综合</t>
         </is>
       </c>
-      <c r="L216" s="15" t="inlineStr">
-        <is>
-          <t>古文字学</t>
-        </is>
-      </c>
-      <c r="M216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -12923,8 +12694,7 @@
           <t>相关学科基础</t>
         </is>
       </c>
-      <c r="L217" s="15" t="inlineStr"/>
-      <c r="M217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -12974,8 +12744,7 @@
           <t>相关学科基础</t>
         </is>
       </c>
-      <c r="L218" s="15" t="inlineStr"/>
-      <c r="M218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -13025,8 +12794,7 @@
           <t>相关学科基础</t>
         </is>
       </c>
-      <c r="L219" s="15" t="inlineStr"/>
-      <c r="M219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -13076,8 +12844,7 @@
           <t>相关学科基础</t>
         </is>
       </c>
-      <c r="L220" s="15" t="inlineStr"/>
-      <c r="M220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -13127,8 +12894,7 @@
           <t>相关学科基础</t>
         </is>
       </c>
-      <c r="L221" s="15" t="inlineStr"/>
-      <c r="M221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -13164,8 +12930,7 @@
           <t>相关学科基础</t>
         </is>
       </c>
-      <c r="L222" s="15" t="inlineStr"/>
-      <c r="M222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -13215,12 +12980,7 @@
           <t>相关学科基础</t>
         </is>
       </c>
-      <c r="L223" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
-      <c r="M223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -13270,8 +13030,7 @@
           <t>相关学科基础</t>
         </is>
       </c>
-      <c r="L224" s="15" t="inlineStr"/>
-      <c r="M224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -13321,8 +13080,7 @@
           <t>相关学科基础</t>
         </is>
       </c>
-      <c r="L225" s="15" t="inlineStr"/>
-      <c r="M225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -13372,8 +13130,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L226" s="15" t="inlineStr"/>
-      <c r="M226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -13423,8 +13180,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L227" s="15" t="inlineStr"/>
-      <c r="M227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -13474,8 +13230,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L228" s="15" t="inlineStr"/>
-      <c r="M228" t="inlineStr"/>
+      <c r="L228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -13525,8 +13280,7 @@
           <t>相关学科的基础知识</t>
         </is>
       </c>
-      <c r="L229" s="15" t="inlineStr"/>
-      <c r="M229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -13576,12 +13330,7 @@
           <t>相关学科的基础知识</t>
         </is>
       </c>
-      <c r="L230" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
-      <c r="M230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -13631,8 +13380,7 @@
           <t>相关学科的基础知识</t>
         </is>
       </c>
-      <c r="L231" s="15" t="inlineStr"/>
-      <c r="M231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -13682,8 +13430,7 @@
           <t>相关学科的基础知识</t>
         </is>
       </c>
-      <c r="L232" s="15" t="inlineStr"/>
-      <c r="M232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -13733,8 +13480,7 @@
           <t>相关学科的基础知识</t>
         </is>
       </c>
-      <c r="L233" s="15" t="inlineStr"/>
-      <c r="M233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -13784,8 +13530,7 @@
           <t>相关学科的基础知识</t>
         </is>
       </c>
-      <c r="L234" s="15" t="inlineStr"/>
-      <c r="M234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -13835,8 +13580,7 @@
           <t>相关学科的基础知识</t>
         </is>
       </c>
-      <c r="L235" s="15" t="inlineStr"/>
-      <c r="M235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -13872,8 +13616,7 @@
           <t>相关学科的基础知识</t>
         </is>
       </c>
-      <c r="L236" s="15" t="inlineStr"/>
-      <c r="M236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -13923,8 +13666,7 @@
           <t>相关学科的基础知识</t>
         </is>
       </c>
-      <c r="L237" s="15" t="inlineStr"/>
-      <c r="M237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -13974,8 +13716,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L238" s="15" t="inlineStr"/>
-      <c r="M238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -14025,8 +13766,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L239" s="15" t="inlineStr"/>
-      <c r="M239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -14062,8 +13802,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L240" s="15" t="inlineStr"/>
-      <c r="M240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -14113,8 +13852,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L241" s="15" t="inlineStr"/>
-      <c r="M241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -14150,8 +13888,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L242" s="15" t="inlineStr"/>
-      <c r="M242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -14187,12 +13924,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L243" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
-      <c r="M243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -14228,8 +13960,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L244" s="15" t="inlineStr"/>
-      <c r="M244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -14279,8 +14010,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L245" s="15" t="inlineStr"/>
-      <c r="M245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -14330,8 +14060,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L246" s="15" t="inlineStr"/>
-      <c r="M246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -14381,8 +14110,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L247" s="15" t="inlineStr"/>
-      <c r="M247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -14432,8 +14160,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L248" s="15" t="inlineStr"/>
-      <c r="M248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -14483,8 +14210,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L249" s="15" t="inlineStr"/>
-      <c r="M249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -14534,8 +14260,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L250" s="15" t="inlineStr"/>
-      <c r="M250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -14585,12 +14310,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L251" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
-      <c r="M251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -14640,8 +14360,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L252" s="15" t="inlineStr"/>
-      <c r="M252" t="inlineStr"/>
+      <c r="L252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -14677,8 +14396,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L253" s="15" t="inlineStr"/>
-      <c r="M253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -14728,8 +14446,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L254" s="15" t="inlineStr"/>
-      <c r="M254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -14779,8 +14496,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L255" s="15" t="inlineStr"/>
-      <c r="M255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -14830,8 +14546,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L256" s="15" t="inlineStr"/>
-      <c r="M256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -14867,8 +14582,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L257" s="15" t="inlineStr"/>
-      <c r="M257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -14904,8 +14618,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L258" s="15" t="inlineStr"/>
-      <c r="M258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -14941,8 +14654,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L259" s="15" t="inlineStr"/>
-      <c r="M259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -14978,8 +14690,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L260" s="15" t="inlineStr"/>
-      <c r="M260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -15015,12 +14726,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L261" s="15" t="inlineStr">
-        <is>
-          <t>生物医药</t>
-        </is>
-      </c>
-      <c r="M261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -15070,8 +14776,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L262" s="15" t="inlineStr"/>
-      <c r="M262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -15111,7 +14816,7 @@
           <t>大类</t>
         </is>
       </c>
-      <c r="M263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -15151,7 +14856,7 @@
           <t>试验班(按科类)</t>
         </is>
       </c>
-      <c r="M264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -15201,8 +14906,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L265" s="15" t="inlineStr"/>
-      <c r="M265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -15252,8 +14956,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L266" s="15" t="inlineStr"/>
-      <c r="M266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -15303,8 +15006,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L267" s="15" t="inlineStr"/>
-      <c r="M267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -15354,12 +15056,7 @@
           <t>语文、历史</t>
         </is>
       </c>
-      <c r="L268" s="15" t="inlineStr">
-        <is>
-          <t>古文字方向</t>
-        </is>
-      </c>
-      <c r="M268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -15409,8 +15106,7 @@
           <t>语文、历史</t>
         </is>
       </c>
-      <c r="L269" s="15" t="inlineStr"/>
-      <c r="M269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -15460,8 +15156,7 @@
           <t>语文、历史</t>
         </is>
       </c>
-      <c r="L270" s="15" t="inlineStr"/>
-      <c r="M270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -15511,8 +15206,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L271" s="15" t="inlineStr"/>
-      <c r="M271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -15562,8 +15256,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L272" s="15" t="inlineStr"/>
-      <c r="M272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -15613,8 +15306,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L273" s="15" t="inlineStr"/>
-      <c r="M273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -15664,8 +15356,7 @@
           <t>数学、物理</t>
         </is>
       </c>
-      <c r="L274" s="15" t="inlineStr"/>
-      <c r="M274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -15715,8 +15406,7 @@
           <t>化学、生物</t>
         </is>
       </c>
-      <c r="L275" s="15" t="inlineStr"/>
-      <c r="M275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -15766,8 +15456,7 @@
           <t>化学、生物</t>
         </is>
       </c>
-      <c r="L276" s="15" t="inlineStr"/>
-      <c r="M276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -15817,8 +15506,7 @@
           <t>化学、生物</t>
         </is>
       </c>
-      <c r="L277" s="15" t="inlineStr"/>
-      <c r="M277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -15868,8 +15556,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L278" s="15" t="inlineStr"/>
-      <c r="M278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -15919,8 +15606,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L279" s="15" t="inlineStr"/>
-      <c r="M279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -15970,8 +15656,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L280" s="15" t="inlineStr"/>
-      <c r="M280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -16021,8 +15706,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L281" s="15" t="inlineStr"/>
-      <c r="M281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -16072,8 +15756,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L282" s="15" t="inlineStr"/>
-      <c r="M282" t="inlineStr"/>
+      <c r="L282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -16123,8 +15806,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L283" s="15" t="inlineStr"/>
-      <c r="M283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -16174,8 +15856,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L284" s="15" t="inlineStr"/>
-      <c r="M284" t="inlineStr"/>
+      <c r="L284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -16225,8 +15906,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L285" s="15" t="inlineStr"/>
-      <c r="M285" t="inlineStr"/>
+      <c r="L285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -16262,8 +15942,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L286" s="15" t="inlineStr"/>
-      <c r="M286" t="inlineStr"/>
+      <c r="L286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -16289,7 +15968,7 @@
       </c>
       <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr"/>
-      <c r="M287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -16325,8 +16004,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L288" s="15" t="inlineStr"/>
-      <c r="M288" t="inlineStr"/>
+      <c r="L288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -16362,8 +16040,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L289" s="15" t="inlineStr"/>
-      <c r="M289" t="inlineStr"/>
+      <c r="L289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -16399,8 +16076,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L290" s="15" t="inlineStr"/>
-      <c r="M290" t="inlineStr"/>
+      <c r="L290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -16450,8 +16126,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L291" s="15" t="inlineStr"/>
-      <c r="M291" t="inlineStr"/>
+      <c r="L291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -16501,8 +16176,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L292" s="15" t="inlineStr"/>
-      <c r="M292" t="inlineStr"/>
+      <c r="L292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -16552,8 +16226,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L293" s="15" t="inlineStr"/>
-      <c r="M293" t="inlineStr"/>
+      <c r="L293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -16603,8 +16276,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L294" s="15" t="inlineStr"/>
-      <c r="M294" t="inlineStr"/>
+      <c r="L294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -16640,12 +16312,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L295" s="15" t="inlineStr">
-        <is>
-          <t>草类植物生物育种</t>
-        </is>
-      </c>
-      <c r="M295" t="inlineStr"/>
+      <c r="L295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -16681,8 +16348,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L296" s="15" t="inlineStr"/>
-      <c r="M296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -16732,8 +16398,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L297" s="15" t="inlineStr"/>
-      <c r="M297" t="inlineStr"/>
+      <c r="L297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -16783,8 +16448,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L298" s="15" t="inlineStr"/>
-      <c r="M298" t="inlineStr"/>
+      <c r="L298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -16834,12 +16498,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L299" s="15" t="inlineStr">
-        <is>
-          <t>古文字学方向</t>
-        </is>
-      </c>
-      <c r="M299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -16873,8 +16532,7 @@
           <t>数学与逻辑、经典物理</t>
         </is>
       </c>
-      <c r="L300" s="15" t="inlineStr"/>
-      <c r="M300" t="inlineStr"/>
+      <c r="L300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -16908,8 +16566,7 @@
           <t>数学与逻辑、经典物理</t>
         </is>
       </c>
-      <c r="L301" s="15" t="inlineStr"/>
-      <c r="M301" t="inlineStr"/>
+      <c r="L301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -16957,8 +16614,7 @@
           <t>数学与逻辑、经典物理</t>
         </is>
       </c>
-      <c r="L302" s="15" t="inlineStr"/>
-      <c r="M302" t="inlineStr"/>
+      <c r="L302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -17008,8 +16664,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L303" s="15" t="inlineStr"/>
-      <c r="M303" t="inlineStr"/>
+      <c r="L303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -17059,8 +16714,7 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L304" s="15" t="inlineStr"/>
-      <c r="M304" t="inlineStr"/>
+      <c r="L304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -17110,22 +16764,18 @@
           <t>无笔试</t>
         </is>
       </c>
-      <c r="L305" s="15" t="inlineStr"/>
-      <c r="M305" t="inlineStr"/>
+      <c r="L305" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="63">
+  <mergeCells count="42">
     <mergeCell ref="K36:K37"/>
-    <mergeCell ref="L139:L146"/>
     <mergeCell ref="K33:K34"/>
-    <mergeCell ref="L78:L79"/>
     <mergeCell ref="C33:C34"/>
     <mergeCell ref="K126:K127"/>
     <mergeCell ref="C104:C105"/>
     <mergeCell ref="C262:C264"/>
     <mergeCell ref="K104:K105"/>
     <mergeCell ref="C29:C32"/>
-    <mergeCell ref="L99:L101"/>
     <mergeCell ref="K112:K123"/>
     <mergeCell ref="K135:K138"/>
     <mergeCell ref="K29:K32"/>
@@ -17135,47 +16785,29 @@
     <mergeCell ref="C286:C287"/>
     <mergeCell ref="K44:K45"/>
     <mergeCell ref="K286:K287"/>
-    <mergeCell ref="L126:L127"/>
     <mergeCell ref="K139:K146"/>
-    <mergeCell ref="L33:L34"/>
     <mergeCell ref="C41:C42"/>
-    <mergeCell ref="L209:L210"/>
     <mergeCell ref="K81:K84"/>
-    <mergeCell ref="L104:L105"/>
     <mergeCell ref="C148:C151"/>
     <mergeCell ref="C36:C37"/>
-    <mergeCell ref="L29:L32"/>
-    <mergeCell ref="L44:L45"/>
     <mergeCell ref="C61:C62"/>
     <mergeCell ref="K61:K62"/>
-    <mergeCell ref="L262:L264"/>
-    <mergeCell ref="L38:L39"/>
-    <mergeCell ref="L41:L42"/>
     <mergeCell ref="C135:C138"/>
     <mergeCell ref="C139:C146"/>
+    <mergeCell ref="K148:K151"/>
     <mergeCell ref="C78:C79"/>
-    <mergeCell ref="L112:L123"/>
+    <mergeCell ref="C209:C210"/>
     <mergeCell ref="K38:K39"/>
-    <mergeCell ref="K148:K151"/>
     <mergeCell ref="K78:K79"/>
-    <mergeCell ref="L81:L84"/>
     <mergeCell ref="K85:K87"/>
+    <mergeCell ref="C112:C123"/>
     <mergeCell ref="C85:C87"/>
-    <mergeCell ref="C112:C123"/>
     <mergeCell ref="C81:C84"/>
-    <mergeCell ref="C209:C210"/>
-    <mergeCell ref="L286:L287"/>
     <mergeCell ref="C38:C39"/>
     <mergeCell ref="K262:K264"/>
-    <mergeCell ref="L61:L62"/>
-    <mergeCell ref="L148:L151"/>
     <mergeCell ref="C99:C101"/>
-    <mergeCell ref="L130:L134"/>
     <mergeCell ref="C126:C127"/>
-    <mergeCell ref="L135:L138"/>
     <mergeCell ref="K99:K101"/>
-    <mergeCell ref="L36:L37"/>
-    <mergeCell ref="L85:L87"/>
     <mergeCell ref="C130:C134"/>
     <mergeCell ref="K130:K134"/>
   </mergeCells>
